--- a/AAII_Financials/Yearly/THNPY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/THNPY_YR_FIN.xlsx
@@ -894,10 +894,10 @@
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>48700</v>
+        <v>97500</v>
       </c>
       <c r="E14" s="3">
-        <v>17700</v>
+        <v>34300</v>
       </c>
       <c r="F14" s="3">
         <v>49500</v>
@@ -972,10 +972,10 @@
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>7906300</v>
+        <v>7857600</v>
       </c>
       <c r="E17" s="3">
-        <v>6504500</v>
+        <v>6487900</v>
       </c>
       <c r="F17" s="3">
         <v>6110600</v>
@@ -1005,10 +1005,10 @@
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>551800</v>
+        <v>600600</v>
       </c>
       <c r="E18" s="3">
-        <v>451600</v>
+        <v>468200</v>
       </c>
       <c r="F18" s="3">
         <v>525400</v>
@@ -1086,10 +1086,10 @@
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>590800</v>
+        <v>639500</v>
       </c>
       <c r="E21" s="3">
-        <v>519900</v>
+        <v>536500</v>
       </c>
       <c r="F21" s="3">
         <v>507000</v>
